--- a/data/italy/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,292 +425,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_red_cards</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_red_cards_against</t>
+          <t>dif_mean_last_30_matches_dangerous_attacks</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.851341919998944</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.1933239380550177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.558187426337004</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.08583894953360664</v>
+        <v>-0.6186863043631206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.7602925291714409</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.3650018371222306</v>
+        <v>-0.8151253918201364</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5353286224362194</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.5422775475407982</v>
+        <v>1.149265482750023</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.4875301814645649</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.5045832809165429</v>
+        <v>1.149265482750023</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1943756878026247</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.1933239380550177</v>
+        <v>0.6090579922432289</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1943756878026247</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.1933239380550177</v>
+        <v>1.36207449416179</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8080909701430954</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.8214404351294223</v>
+        <v>0.0197407298721812</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>WUqjkmPH</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3170537141477675</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.3301064761736526</v>
+        <v>-0.4386171408608559</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>8SWavWAa</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3404983740741652</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.04377239113254056</v>
+        <v>0.2325497412839484</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>z3jsi9f5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.3170537141477675</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.3301064761736526</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-1.339912518048552</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.3301064761736526</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.6239113553180029</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.062909056093791</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OC8I1VXq</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.7058050897530168</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.8535368904023231</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WxCQa92d</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.1943756878026247</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.1933239380550177</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Whh3dzd4</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.8762815570698143</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.8912311570265784</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.217234491703409</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.1933239380550177</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.217234491703409</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-2.2870455949697</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.2966615681927032</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.5394786418651207</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>OAeKROjD</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>-1.169436050731754</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.202490499888103</v>
+        <v>1.182005330659525</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,7 +438,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -448,111 +448,131 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.6581677641074828</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.6186863043631206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.8151253918201364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.149265482750023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.149265482750023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6090579922432289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.36207449416179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0197407298721812</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.4386171408608559</v>
+        <v>-0.6186863043631206</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2325497412839484</v>
+        <v>-0.8151253918201364</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.182005330659525</v>
+        <v>1.149265482750023</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.149265482750023</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.6090579922432289</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,154 +425,762 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_dangerous_attacks</t>
+          <t>dif_mean_last_60_matches_attacks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP_against</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>WIDwXGr3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0.6660536911657959</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.95749951069505</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.7951194906694748</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.4457920606377364</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1.20757421241802</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.013217841902685</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3244323297452965</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.591792039962583</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>4CLi9Djd</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6581677641074828</v>
+        <v>1.203496718894561</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.3244290964969024</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6078811318460915</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.310365611811077</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.7706844178622821</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.346794238266383</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.04554309133768435</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1.05373265236705</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.4116871334572335</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9996820501502441</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.2431192457453176</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8292265234689363</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.8479328577516209</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.7419717606586362</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>fB59P6ff</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1.797353907972557</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.979568029805835</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2628809787684932</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.504298054990446</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.862908904251628</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.3210877435521076</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.857542306206655</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4634501521821301</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>jwaINpP6</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-2.865524761825039</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.279656158575819</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.577119837645364</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.970295466591462</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3215400685270635</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.3210877435521076</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1.120426050769305</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.270434324854282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2g2mKBIE</t>
+          <t>xY3xTu1n</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1.313470272427523</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.367930235018962</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4731193477970498</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.430650383896612</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.6146523483780899</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6319876746298871</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-2.275831438340352</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.261174391884083</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>OjcQLOgJ</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.777839383712858</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.02457539122882023</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-0.1821700556207624</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.3464976156076882</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1971192253349712</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.5660768327232716</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8416469668077043</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.5328822809258842</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.591838703122462</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2642849091889334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1.225491429601154</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.01546982894590157</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3088809991788396</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5405430704636519</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.134759246658731</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.161474018064329</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5735355957734335</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2839409876186421</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.6186863043631206</v>
+        <v>1.797353907972557</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.4127031729400455</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.826881672720272</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.205222516466666</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3215400685270635</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.062368624360326</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.1201172522297816</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-2.747514895600019</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.8151253918201364</v>
+        <v>1.709375065146187</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.7216624404910462</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.792882101337547</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.08346093653861836</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1030951712491944</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.09870347930964227</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8832685224081391</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.157086742591008</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.149265482750023</v>
+        <v>-1.567836830136086</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.3464976156076882</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.784119929491923</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1315748453728324</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.134759246658731</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.161474018064329</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1508381256170023</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.515454164200188</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.149265482750023</v>
+        <v>-1.743794515788825</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.911407973707101</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.945120000928136</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.743390791319004</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7584298630828017</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.7658562720370384</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.119135533873708</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.57051214013532</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6090579922432289</v>
+        <v>1.401449115253893</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-2.045773587138193</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.458881509437501</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.79298150799573</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.1153497260286747</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1236807849328232</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.304237091687787</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-4.920959529637039</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.5216606869901956</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.560266166700906</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5848811216409182</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.08346093653861836</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.959876798111082</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.8770484041582712</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.770647036136435</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.1467350884944564</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-1.281905590950384</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.102668472667244</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.7184527899855643</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2438406326526654</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3215400685270635</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.3210877435521076</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8770541961183675</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.03526167056343001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>dGwq9oAD</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-1.611826251549271</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.566546907016034</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.163119653952246</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.272643788495358</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.19531965763854</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.210624800521969</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-4.852224949460504</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.05625901763174035</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AJ5eIkmR</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.116185923500985</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.2361550200537593</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1478809277426271</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9013973867202575</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.2245721746676093</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.3210877435521076</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-1.137406783423877</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.8264309185912154</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>8Kjh0jRr</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-1.941746912148157</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.220367241258102</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-2.037120041748829</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.4683722072123309</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-2.955133390640974</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.902754898872546</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.0618565062189479</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.937423285668889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2g2mKBIE</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.1257558942715317</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.132093164814959</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.025119592721207</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.056131198741395</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.231727140518185</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.24768884456238</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-3.563275681695259</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.2721499185201052</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SznSCTAl</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.1821700556207624</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.074758746263619</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.2431192457453176</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.08346093653861836</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9768747603606711</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.09870347930964227</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.605163578133513</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5598900422396587</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.4461065840998716</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.560266166700906</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.3351192865660105</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.514690140508941</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.1881646917879646</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.2719369610944668</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.7630981352655806</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8677204258211082</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-1.369884433776754</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.477833297550602</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.503786028070614</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.5245051008522471</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.824832567020207</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.04859530466613205</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,713 +473,868 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WIDwXGr3</t>
+          <t>EssDGebM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6660536911657959</v>
+        <v>-0.8860007982317203</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.95749951069505</v>
+        <v>-0.01546982894590157</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.7951194906694748</v>
+        <v>0.1478809277426271</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4457920606377364</v>
+        <v>0.4202582983781168</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.20757421241802</v>
+        <v>-1.316796661056955</v>
       </c>
       <c r="G2" t="n">
-        <v>1.013217841902685</v>
+        <v>0.2348729170540559</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3244323297452965</v>
+        <v>-1.113286834575392</v>
       </c>
       <c r="I2" t="n">
-        <v>0.591792039962583</v>
+        <v>-0.8354508286616851</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4CLi9Djd</t>
+          <t>rcXrBZLq</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.203496718894561</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3244290964969024</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6078811318460915</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.310365611811077</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7706844178622821</v>
+        <v>-0.2245721746676093</v>
       </c>
       <c r="G3" t="n">
-        <v>1.346794238266383</v>
+        <v>-0.209895611430875</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.04554309133768435</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.05373265236705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Ug79dz7j</t>
+          <t>Y96v2dqT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4116871334572335</v>
+        <v>2.237248122104406</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9996820501502441</v>
+        <v>-1.11889578448519</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2431192457453176</v>
+        <v>0.9988813053340363</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8292265234689363</v>
+        <v>-0.8307033313114489</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1.862908904251628</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1.902754898872546</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8479328577516209</v>
+        <v>0.7666445939099694</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7419717606586362</v>
+        <v>-2.89828328524304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fB59P6ff</t>
+          <t>0b5fTYsS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.797353907972557</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.979568029805835</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2628809787684932</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.504298054990446</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.862908904251628</v>
+        <v>0.1030951712491944</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3210877435521076</v>
+        <v>-0.09870347930964227</v>
       </c>
       <c r="H5" t="n">
-        <v>4.857542306206655</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4634501521821301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
+          <t>IFm4IHT9</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-2.865524761825039</v>
+        <v>-3.657334347262367</v>
       </c>
       <c r="C6" t="n">
-        <v>2.279656158575819</v>
+        <v>1.838285776360103</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.577119837645364</v>
+        <v>-2.635120307083332</v>
       </c>
       <c r="E6" t="n">
-        <v>2.970295466591462</v>
+        <v>1.382536475062398</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3215400685270635</v>
+        <v>-0.4066095890658336</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3210877435521076</v>
+        <v>-1.062368624360326</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.120426050769305</v>
+        <v>-1.682717068837148</v>
       </c>
       <c r="I6" t="n">
-        <v>6.270434324854282</v>
+        <v>0.6759063134618456</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
+          <t>WIDwXGr3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.313470272427523</v>
+        <v>-0.6660536911657959</v>
       </c>
       <c r="C7" t="n">
-        <v>2.367930235018962</v>
+        <v>-1.95749951069505</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4731193477970498</v>
+        <v>-0.7951194906694748</v>
       </c>
       <c r="E7" t="n">
-        <v>1.430650383896612</v>
+        <v>-0.4457920606377364</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6146523483780899</v>
+        <v>-1.20757421241802</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6319876746298871</v>
+        <v>1.013217841902685</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.275831438340352</v>
+        <v>0.3244323297452965</v>
       </c>
       <c r="I7" t="n">
-        <v>1.261174391884083</v>
+        <v>0.591792039962583</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
+          <t>4CLi9Djd</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1.203496718894561</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0.3244290964969024</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.6078811318460915</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.310365611811077</v>
       </c>
       <c r="F8" t="n">
-        <v>1.777839383712858</v>
+        <v>-0.7706844178622821</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.02457539122882023</v>
+        <v>1.346794238266383</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.04554309133768435</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-1.05373265236705</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1821700556207624</v>
+        <v>0.4116871334572335</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3464976156076882</v>
+        <v>0.9996820501502441</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1971192253349712</v>
+        <v>-0.2431192457453176</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5660768327232716</v>
+        <v>0.8292265234689363</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8416469668077043</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5328822809258842</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.591838703122462</v>
+        <v>-0.8479328577516209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2642849091889334</v>
+        <v>-0.7419717606586362</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
+          <t>fB59P6ff</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.225491429601154</v>
+        <v>1.797353907972557</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.01546982894590157</v>
+        <v>-1.979568029805835</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3088809991788396</v>
+        <v>0.2628809787684932</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5405430704636519</v>
+        <v>-1.504298054990446</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.134759246658731</v>
+        <v>-1.862908904251628</v>
       </c>
       <c r="G10" t="n">
-        <v>1.161474018064329</v>
+        <v>-0.3210877435521076</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5735355957734335</v>
+        <v>4.857542306206655</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2839409876186421</v>
+        <v>0.4634501521821301</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8f71RSPs</t>
+          <t>jwaINpP6</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.797353907972557</v>
+        <v>-2.865524761825039</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.4127031729400455</v>
+        <v>2.279656158575819</v>
       </c>
       <c r="D11" t="n">
-        <v>1.826881672720272</v>
+        <v>-1.577119837645364</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.205222516466666</v>
+        <v>2.970295466591462</v>
       </c>
       <c r="F11" t="n">
         <v>0.3215400685270635</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.062368624360326</v>
+        <v>-0.3210877435521076</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1201172522297816</v>
+        <v>-1.120426050769305</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.747514895600019</v>
+        <v>6.270434324854282</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>UuMqRJVb</t>
+          <t>xY3xTu1n</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.709375065146187</v>
+        <v>1.313470272427523</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.7216624404910462</v>
+        <v>2.367930235018962</v>
       </c>
       <c r="D12" t="n">
-        <v>2.792882101337547</v>
+        <v>-0.4731193477970498</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08346093653861836</v>
+        <v>1.430650383896612</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1030951712491944</v>
+        <v>-0.6146523483780899</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.09870347930964227</v>
+        <v>0.6319876746298871</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8832685224081391</v>
+        <v>-2.275831438340352</v>
       </c>
       <c r="I12" t="n">
-        <v>0.157086742591008</v>
+        <v>1.261174391884083</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bLD0NyVN</t>
+          <t>OjcQLOgJ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.567836830136086</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.3464976156076882</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.784119929491923</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1315748453728324</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.134759246658731</v>
+        <v>1.777839383712858</v>
       </c>
       <c r="G13" t="n">
-        <v>1.161474018064329</v>
+        <v>-0.02457539122882023</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1508381256170023</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.515454164200188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.743794515788825</v>
+        <v>-0.1821700556207624</v>
       </c>
       <c r="C14" t="n">
-        <v>0.911407973707101</v>
+        <v>-0.3464976156076882</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.945120000928136</v>
+        <v>-0.1971192253349712</v>
       </c>
       <c r="E14" t="n">
-        <v>1.743390791319004</v>
+        <v>-0.5660768327232716</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7584298630828017</v>
+        <v>0.8416469668077043</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7658562720370384</v>
+        <v>-0.5328822809258842</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.119135533873708</v>
+        <v>1.591838703122462</v>
       </c>
       <c r="I14" t="n">
-        <v>1.57051214013532</v>
+        <v>0.2642849091889334</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>McP0d8Q7</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.401449115253893</v>
+        <v>1.225491429601154</v>
       </c>
       <c r="C15" t="n">
-        <v>-2.045773587138193</v>
+        <v>-0.01546982894590157</v>
       </c>
       <c r="D15" t="n">
-        <v>1.458881509437501</v>
+        <v>0.3088809991788396</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.79298150799573</v>
+        <v>0.5405430704636519</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1153497260286747</v>
+        <v>-1.134759246658731</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1236807849328232</v>
+        <v>1.161474018064329</v>
       </c>
       <c r="H15" t="n">
-        <v>4.304237091687787</v>
+        <v>0.5735355957734335</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.920959529637039</v>
+        <v>0.2839409876186421</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5216606869901956</v>
+        <v>1.797353907972557</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.560266166700906</v>
+        <v>-0.4127031729400455</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5848811216409182</v>
+        <v>1.826881672720272</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08346093653861836</v>
+        <v>-0.205222516466666</v>
       </c>
       <c r="F16" t="n">
-        <v>1.959876798111082</v>
+        <v>0.3215400685270635</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8770484041582712</v>
+        <v>-1.062368624360326</v>
       </c>
       <c r="H16" t="n">
-        <v>1.770647036136435</v>
+        <v>-0.1201172522297816</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1467350884944564</v>
+        <v>-2.747514895600019</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.281905590950384</v>
+        <v>1.709375065146187</v>
       </c>
       <c r="C17" t="n">
-        <v>1.102668472667244</v>
+        <v>-0.7216624404910462</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7184527899855643</v>
+        <v>2.792882101337547</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2438406326526654</v>
+        <v>0.08346093653861836</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3215400685270635</v>
+        <v>0.1030951712491944</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3210877435521076</v>
+        <v>-0.09870347930964227</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8770541961183675</v>
+        <v>0.8832685224081391</v>
       </c>
       <c r="I17" t="n">
-        <v>0.03526167056343001</v>
+        <v>0.157086742591008</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.611826251549271</v>
+        <v>-1.567836830136086</v>
       </c>
       <c r="C18" t="n">
-        <v>2.566546907016034</v>
+        <v>-0.3464976156076882</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.163119653952246</v>
+        <v>-1.784119929491923</v>
       </c>
       <c r="E18" t="n">
-        <v>2.272643788495358</v>
+        <v>0.1315748453728324</v>
       </c>
       <c r="F18" t="n">
-        <v>1.19531965763854</v>
+        <v>-1.134759246658731</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.210624800521969</v>
+        <v>1.161474018064329</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.852224949460504</v>
+        <v>0.1508381256170023</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.05625901763174035</v>
+        <v>0.515454164200188</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.116185923500985</v>
+        <v>-1.743794515788825</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.2361550200537593</v>
+        <v>0.911407973707101</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1478809277426271</v>
+        <v>-1.945120000928136</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9013973867202575</v>
+        <v>1.743390791319004</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2245721746676093</v>
+        <v>0.7584298630828017</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3210877435521076</v>
+        <v>-0.7658562720370384</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.137406783423877</v>
+        <v>-1.119135533873708</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8264309185912154</v>
+        <v>1.57051214013532</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.941746912148157</v>
+        <v>1.401449115253893</v>
       </c>
       <c r="C20" t="n">
-        <v>1.220367241258102</v>
+        <v>-2.045773587138193</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.037120041748829</v>
+        <v>1.458881509437501</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4683722072123309</v>
+        <v>-1.79298150799573</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.955133390640974</v>
+        <v>-0.1153497260286747</v>
       </c>
       <c r="G20" t="n">
-        <v>1.902754898872546</v>
+        <v>0.1236807849328232</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0618565062189479</v>
+        <v>4.304237091687787</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.937423285668889</v>
+        <v>-4.920959529637039</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2g2mKBIE</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1257558942715317</v>
+        <v>0.5216606869901956</v>
       </c>
       <c r="C21" t="n">
-        <v>1.132093164814959</v>
+        <v>-1.560266166700906</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.025119592721207</v>
+        <v>0.5848811216409182</v>
       </c>
       <c r="E21" t="n">
-        <v>2.056131198741395</v>
+        <v>0.08346093653861836</v>
       </c>
       <c r="F21" t="n">
-        <v>1.231727140518185</v>
+        <v>1.959876798111082</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.24768884456238</v>
+        <v>-0.8770484041582712</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.563275681695259</v>
+        <v>1.770647036136435</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2721499185201052</v>
+        <v>-0.1467350884944564</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1821700556207624</v>
+        <v>-1.281905590950384</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.074758746263619</v>
+        <v>1.102668472667244</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2431192457453176</v>
+        <v>-0.7184527899855643</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08346093653861836</v>
+        <v>0.2438406326526654</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9768747603606711</v>
+        <v>0.3215400685270635</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.09870347930964227</v>
+        <v>-0.3210877435521076</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.605163578133513</v>
+        <v>0.8770541961183675</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5598900422396587</v>
+        <v>0.03526167056343001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4461065840998716</v>
+        <v>-1.611826251549271</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.560266166700906</v>
+        <v>2.566546907016034</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3351192865660105</v>
+        <v>-1.163119653952246</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.514690140508941</v>
+        <v>2.272643788495358</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1881646917879646</v>
+        <v>1.19531965763854</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2719369610944668</v>
+        <v>-1.210624800521969</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7630981352655806</v>
+        <v>-4.852224949460504</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8677204258211082</v>
+        <v>-0.05625901763174035</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
+          <t>AJ5eIkmR</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.116185923500985</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.2361550200537593</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.1478809277426271</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9013973867202575</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.2245721746676093</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.3210877435521076</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.137406783423877</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.8264309185912154</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>8Kjh0jRr</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-1.941746912148157</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.220367241258102</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.037120041748829</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.4683722072123309</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-2.955133390640974</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.902754898872546</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.0618565062189479</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.937423285668889</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2g2mKBIE</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.1257558942715317</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.132093164814959</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.025119592721207</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.056131198741395</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.231727140518185</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.24768884456238</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-3.563275681695259</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.2721499185201052</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>SznSCTAl</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.1821700556207624</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-1.074758746263619</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.2431192457453176</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.08346093653861836</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9768747603606711</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.09870347930964227</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.605163578133513</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5598900422396587</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.4461065840998716</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.560266166700906</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.3351192865660105</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-2.514690140508941</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.1881646917879646</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.2719369610944668</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7630981352655806</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8677204258211082</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
           <t>EXLhbUee</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B29" t="n">
         <v>-1.369884433776754</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C29" t="n">
         <v>1.477833297550602</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D29" t="n">
         <v>-0.503786028070614</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E29" t="n">
         <v>0.5245051008522471</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>-0.824832567020207</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I29" t="n">
         <v>0.04859530466613205</v>
       </c>
     </row>
